--- a/inputs/radar.xlsx
+++ b/inputs/radar.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E91DD1-EEA0-412F-BC8C-1F251F419058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E5EE66-DB86-4634-9965-74148434E915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9285" yWindow="3225" windowWidth="16815" windowHeight="11055" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
+    <workbookView xWindow="29940" yWindow="2040" windowWidth="15165" windowHeight="9750" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Pri</t>
   </si>
@@ -69,6 +71,9 @@
   </si>
   <si>
     <t>duty</t>
+  </si>
+  <si>
+    <t>pwEnum</t>
   </si>
 </sst>
 </file>
@@ -76,13 +81,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="0.0E+00"/>
-    <numFmt numFmtId="171" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0E+00"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -108,12 +119,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,102 +440,325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21C0482-AC5F-49E4-B7B5-F9FEEC654263}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5.28515625" customWidth="1"/>
-    <col min="8" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" customWidth="1"/>
+    <col min="9" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C2" s="1">
+        <f>B2*F2</f>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E2" s="4">
+        <f>1/F2</f>
+        <v>0.01</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>64</v>
+      </c>
+      <c r="J2" s="2">
+        <v>64</v>
+      </c>
+      <c r="K2" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L2" s="2">
+        <v>120</v>
+      </c>
+      <c r="M2" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>1.25E-3</v>
       </c>
-      <c r="B2" s="1">
-        <f>A2*E2</f>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C7" si="0">B3*F3</f>
         <v>0.25</v>
       </c>
-      <c r="C2" s="3">
-        <v>8000000000</v>
-      </c>
-      <c r="D2" s="4">
-        <f>1/E2</f>
+      <c r="D3" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E7" si="1">1/F3</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F3">
         <v>200</v>
       </c>
-      <c r="F2" s="3">
-        <v>150000000</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="G3" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>64</v>
+      </c>
+      <c r="J3" s="2">
+        <v>64</v>
+      </c>
+      <c r="K3" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L3" s="2">
+        <v>100</v>
+      </c>
+      <c r="M3" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F4">
+        <v>400</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="H2" s="2">
-        <v>64</v>
-      </c>
-      <c r="I2" s="2">
-        <v>64</v>
-      </c>
-      <c r="J2" s="2">
-        <v>4500</v>
-      </c>
-      <c r="K2" s="2">
-        <v>40</v>
-      </c>
-      <c r="L2" s="2">
-        <v>40</v>
+      <c r="I4" s="2">
+        <v>64</v>
+      </c>
+      <c r="J4" s="2">
+        <v>64</v>
+      </c>
+      <c r="K4" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L4" s="2">
+        <v>100</v>
+      </c>
+      <c r="M4" s="2">
+        <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H13" s="1"/>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.25E-3</v>
+      </c>
+      <c r="F5">
+        <v>800</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>64</v>
+      </c>
+      <c r="J5" s="2">
+        <v>64</v>
+      </c>
+      <c r="K5" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L5" s="2">
+        <v>90</v>
+      </c>
+      <c r="M5" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1.56E-4</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24959999999999999</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="F6">
+        <v>1600</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>64</v>
+      </c>
+      <c r="J6" s="2">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L6" s="2">
+        <v>70</v>
+      </c>
+      <c r="M6" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>7.7999999999999999E-5</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24959999999999999</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="1"/>
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="F7">
+        <v>3200</v>
+      </c>
+      <c r="G7" s="5">
+        <v>10000000</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>64</v>
+      </c>
+      <c r="J7" s="2">
+        <v>64</v>
+      </c>
+      <c r="K7" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>60</v>
+      </c>
+      <c r="M7" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/inputs/radar.xlsx
+++ b/inputs/radar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E5EE66-DB86-4634-9965-74148434E915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3394650B-0273-4214-B694-E040D38C6B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="2040" windowWidth="15165" windowHeight="9750" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
+    <workbookView xWindow="32700" yWindow="2310" windowWidth="17580" windowHeight="8955" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Pri</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>pwEnum</t>
+  </si>
+  <si>
+    <t>noiseFigure</t>
   </si>
 </sst>
 </file>
@@ -440,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21C0482-AC5F-49E4-B7B5-F9FEEC654263}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
@@ -452,9 +455,10 @@
     <col min="11" max="11" width="10.42578125" customWidth="1"/>
     <col min="12" max="12" width="7.85546875" customWidth="1"/>
     <col min="13" max="13" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -494,8 +498,11 @@
       <c r="M1" t="s">
         <v>5</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -507,7 +514,7 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="3">
-        <v>9000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="E2" s="4">
         <f>1/F2</f>
@@ -532,13 +539,16 @@
         <v>450000</v>
       </c>
       <c r="L2" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M2" s="2">
-        <v>120</v>
+        <v>100</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -580,8 +590,11 @@
       <c r="M3" s="2">
         <v>100</v>
       </c>
+      <c r="N3" s="5">
+        <v>1E-3</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -623,8 +636,11 @@
       <c r="M4" s="2">
         <v>100</v>
       </c>
+      <c r="N4" s="5">
+        <v>1E-3</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -666,8 +682,11 @@
       <c r="M5" s="2">
         <v>90</v>
       </c>
+      <c r="N5" s="5">
+        <v>1E-3</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -709,8 +728,11 @@
       <c r="M6" s="2">
         <v>70</v>
       </c>
+      <c r="N6" s="5">
+        <v>1E-3</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -752,8 +774,11 @@
       <c r="M7" s="2">
         <v>60</v>
       </c>
+      <c r="N7" s="5">
+        <v>1E-3</v>
+      </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I13" s="1"/>
     </row>
   </sheetData>

--- a/inputs/radar.xlsx
+++ b/inputs/radar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3394650B-0273-4214-B694-E040D38C6B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309BA118-4BA9-4674-9DB9-EA1601DD5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32700" yWindow="2310" windowWidth="17580" windowHeight="8955" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
+    <workbookView xWindow="38010" yWindow="660" windowWidth="14505" windowHeight="8235" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -443,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21C0482-AC5F-49E4-B7B5-F9FEEC654263}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
@@ -503,14 +503,13 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="C2" s="1">
-        <f>B2*F2</f>
+        <v>0.01</v>
+      </c>
+      <c r="C2">
         <v>0.25</v>
       </c>
       <c r="D2" s="3">
@@ -518,56 +517,55 @@
       </c>
       <c r="E2" s="4">
         <f>1/F2</f>
-        <v>0.01</v>
-      </c>
-      <c r="F2" s="2">
-        <v>100</v>
+        <v>0.04</v>
+      </c>
+      <c r="F2">
+        <v>25</v>
       </c>
       <c r="G2" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="H2" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
-        <v>64</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="I2">
+        <v>64</v>
+      </c>
+      <c r="J2">
         <v>64</v>
       </c>
       <c r="K2" s="2">
         <v>450000</v>
       </c>
-      <c r="L2" s="2">
-        <v>100</v>
-      </c>
-      <c r="M2" s="2">
-        <v>100</v>
+      <c r="L2">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>35</v>
       </c>
       <c r="N2" s="5">
         <v>1E-4</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>1.25E-3</v>
-      </c>
-      <c r="C3" s="1">
-        <f t="shared" ref="C3:C7" si="0">B3*F3</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C3">
         <v>0.25</v>
       </c>
       <c r="D3" s="3">
-        <v>9000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" ref="E3:E7" si="1">1/F3</f>
-        <v>5.0000000000000001E-3</v>
+        <f>1/F3</f>
+        <v>0.02</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G3" s="3">
         <v>1000000</v>
@@ -575,211 +573,303 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="2">
-        <v>64</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="I3">
+        <v>64</v>
+      </c>
+      <c r="J3">
         <v>64</v>
       </c>
       <c r="K3" s="2">
         <v>450000</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C4" s="1">
+        <f>B4*F4</f>
+        <v>0.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9500000000</v>
+      </c>
+      <c r="E4" s="4">
+        <f>1/F4</f>
+        <v>0.01</v>
+      </c>
+      <c r="F4" s="2">
         <v>100</v>
       </c>
-      <c r="M3" s="2">
+      <c r="G4" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>64</v>
+      </c>
+      <c r="J4" s="2">
+        <v>64</v>
+      </c>
+      <c r="K4" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L4" s="2">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2">
+        <v>30</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1.25E-3</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" ref="C5:C9" si="0">B5*F5</f>
+        <v>0.25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9000000000</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" ref="E5:E9" si="1">1/F5</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F5">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>64</v>
+      </c>
+      <c r="J5" s="2">
+        <v>64</v>
+      </c>
+      <c r="K5" s="2">
+        <v>450000</v>
+      </c>
+      <c r="L5" s="2">
         <v>100</v>
       </c>
-      <c r="N3" s="5">
+      <c r="M5" s="2">
+        <v>100</v>
+      </c>
+      <c r="N5" s="5">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
         <v>6.2500000000000001E-4</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D6" s="3">
         <v>9000000000</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <f t="shared" si="1"/>
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F4">
+      <c r="F6">
         <v>400</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G6" s="3">
         <v>1000000</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
-        <v>64</v>
-      </c>
-      <c r="J4" s="2">
-        <v>64</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>64</v>
+      </c>
+      <c r="J6" s="2">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2">
         <v>450000</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L6" s="2">
         <v>100</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M6" s="2">
         <v>100</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N6" s="5">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
         <v>3.1250000000000001E-4</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D7" s="3">
         <v>9000000000</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E7" s="4">
         <f t="shared" si="1"/>
         <v>1.25E-3</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>800</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G7" s="3">
         <v>1000000</v>
       </c>
-      <c r="H5">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I5" s="2">
-        <v>64</v>
-      </c>
-      <c r="J5" s="2">
-        <v>64</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="I7" s="2">
+        <v>64</v>
+      </c>
+      <c r="J7" s="2">
+        <v>64</v>
+      </c>
+      <c r="K7" s="2">
         <v>450000</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L7" s="2">
         <v>90</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M7" s="2">
         <v>90</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N7" s="5">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
         <v>1.56E-4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.24959999999999999</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D8" s="3">
         <v>9000000000</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
         <v>6.2500000000000001E-4</v>
       </c>
-      <c r="F6">
+      <c r="F8">
         <v>1600</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G8" s="3">
         <v>1000000</v>
       </c>
-      <c r="H6">
+      <c r="H8">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
-        <v>64</v>
-      </c>
-      <c r="J6" s="2">
-        <v>64</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="I8" s="2">
+        <v>64</v>
+      </c>
+      <c r="J8" s="2">
+        <v>64</v>
+      </c>
+      <c r="K8" s="2">
         <v>450000</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L8" s="2">
         <v>70</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M8" s="2">
         <v>70</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N8" s="5">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
         <v>7.7999999999999999E-5</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.24959999999999999</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D9" s="3">
         <v>9000000000</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E9" s="4">
         <f t="shared" si="1"/>
         <v>3.1250000000000001E-4</v>
       </c>
-      <c r="F7">
+      <c r="F9">
         <v>3200</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G9" s="5">
         <v>10000000</v>
       </c>
-      <c r="H7">
+      <c r="H9">
         <v>1</v>
       </c>
-      <c r="I7" s="2">
-        <v>64</v>
-      </c>
-      <c r="J7" s="2">
-        <v>64</v>
-      </c>
-      <c r="K7" s="2">
-        <v>450000</v>
-      </c>
-      <c r="L7" s="2">
-        <v>60</v>
-      </c>
-      <c r="M7" s="2">
-        <v>60</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I13" s="1"/>
+      <c r="I9" s="2">
+        <v>64</v>
+      </c>
+      <c r="J9" s="2">
+        <v>64</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10</v>
+      </c>
+      <c r="L9" s="2">
+        <v>30</v>
+      </c>
+      <c r="M9" s="2">
+        <v>30</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/inputs/radar.xlsx
+++ b/inputs/radar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309BA118-4BA9-4674-9DB9-EA1601DD5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746B26C6-22FA-4652-873C-23B57A720564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38010" yWindow="660" windowWidth="14505" windowHeight="8235" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
+    <workbookView xWindow="35715" yWindow="2715" windowWidth="18120" windowHeight="8235" xr2:uid="{E49E1DF9-4937-4C6D-9A78-CA6266DF6DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Pri</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>noiseFigure</t>
+  </si>
+  <si>
+    <t>minTgtRng</t>
+  </si>
+  <si>
+    <t>maxTgtRng</t>
   </si>
 </sst>
 </file>
@@ -443,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21C0482-AC5F-49E4-B7B5-F9FEEC654263}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
@@ -456,9 +462,11 @@
     <col min="12" max="12" width="7.85546875" customWidth="1"/>
     <col min="13" max="13" width="7.140625" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -501,8 +509,14 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -546,8 +560,14 @@
       <c r="N2" s="5">
         <v>1E-4</v>
       </c>
+      <c r="O2">
+        <v>2000</v>
+      </c>
+      <c r="P2">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -591,8 +611,14 @@
       <c r="N3" s="5">
         <v>1E-4</v>
       </c>
+      <c r="O3">
+        <v>1000</v>
+      </c>
+      <c r="P3">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -637,8 +663,14 @@
       <c r="N4" s="5">
         <v>1E-4</v>
       </c>
+      <c r="O4" s="2">
+        <v>550</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -683,8 +715,14 @@
       <c r="N5" s="5">
         <v>1E-3</v>
       </c>
+      <c r="O5" s="2">
+        <v>270</v>
+      </c>
+      <c r="P5" s="2">
+        <v>550</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -729,8 +767,14 @@
       <c r="N6" s="5">
         <v>1E-3</v>
       </c>
+      <c r="O6" s="2">
+        <v>135</v>
+      </c>
+      <c r="P6" s="2">
+        <v>270</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -775,8 +819,14 @@
       <c r="N7" s="5">
         <v>1E-3</v>
       </c>
+      <c r="O7" s="2">
+        <v>65</v>
+      </c>
+      <c r="P7" s="2">
+        <v>135</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -821,8 +871,14 @@
       <c r="N8" s="5">
         <v>1E-3</v>
       </c>
+      <c r="O8" s="2">
+        <v>30</v>
+      </c>
+      <c r="P8" s="2">
+        <v>65</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -834,7 +890,7 @@
         <v>0.24959999999999999</v>
       </c>
       <c r="D9" s="3">
-        <v>9000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="1"/>
@@ -856,19 +912,25 @@
         <v>64</v>
       </c>
       <c r="K9" s="2">
-        <v>10</v>
+        <v>450000</v>
       </c>
       <c r="L9" s="2">
+        <v>50</v>
+      </c>
+      <c r="M9" s="2">
+        <v>50</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="O9" s="2">
+        <v>20</v>
+      </c>
+      <c r="P9" s="2">
         <v>30</v>
       </c>
-      <c r="M9" s="2">
-        <v>30</v>
-      </c>
-      <c r="N9" s="5">
-        <v>1</v>
-      </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I15" s="1"/>
     </row>
   </sheetData>
